--- a/artfynd/A 8621-2026 artfynd.xlsx
+++ b/artfynd/A 8621-2026 artfynd.xlsx
@@ -785,7 +785,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131758051</v>
+        <v>131758034</v>
       </c>
       <c r="B3" t="n">
         <v>57899</v>
@@ -818,7 +818,7 @@
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -828,10 +828,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>774217</v>
+        <v>774190</v>
       </c>
       <c r="R3" t="n">
-        <v>7125691</v>
+        <v>7125644</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -868,7 +868,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>färska ringhack på gran</t>
+          <t>äldre ringhack högt upp i gran</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -895,7 +895,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131758034</v>
+        <v>131758051</v>
       </c>
       <c r="B4" t="n">
         <v>57899</v>
@@ -928,7 +928,7 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -938,10 +938,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>774190</v>
+        <v>774217</v>
       </c>
       <c r="R4" t="n">
-        <v>7125644</v>
+        <v>7125691</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -978,7 +978,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>äldre ringhack högt upp i gran</t>
+          <t>färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1641,10 +1641,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131757839</v>
+        <v>131758963</v>
       </c>
       <c r="B11" t="n">
-        <v>57899</v>
+        <v>79261</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1652,31 +1652,30 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1684,10 +1683,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>774162</v>
+        <v>774329</v>
       </c>
       <c r="R11" t="n">
-        <v>7125616</v>
+        <v>7125645</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1714,17 +1713,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>förska ringhack på gran</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1733,6 +1727,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1751,10 +1746,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131758963</v>
+        <v>131757839</v>
       </c>
       <c r="B12" t="n">
-        <v>79261</v>
+        <v>57899</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1762,30 +1757,31 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1793,10 +1789,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>774329</v>
+        <v>774162</v>
       </c>
       <c r="R12" t="n">
-        <v>7125645</v>
+        <v>7125616</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1823,12 +1819,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>förska ringhack på gran</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1837,7 +1838,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -2185,10 +2185,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131759091</v>
+        <v>131758780</v>
       </c>
       <c r="B16" t="n">
-        <v>83107</v>
+        <v>57899</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2196,30 +2196,27 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2227,10 +2224,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>774532</v>
+        <v>774139</v>
       </c>
       <c r="R16" t="n">
-        <v>7125635</v>
+        <v>7125579</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2257,21 +2254,25 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>bortfläkt bark på gran, kan vara gjort av tretåig hackspett som bevisligen födosöker i denna skog</t>
         </is>
       </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF16" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2290,10 +2291,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131758780</v>
+        <v>131759091</v>
       </c>
       <c r="B17" t="n">
-        <v>57899</v>
+        <v>83107</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2301,27 +2302,30 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2329,10 +2333,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>774139</v>
+        <v>774532</v>
       </c>
       <c r="R17" t="n">
-        <v>7125579</v>
+        <v>7125635</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2359,25 +2363,21 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>bortfläkt bark på gran, kan vara gjort av tretåig hackspett som bevisligen födosöker i denna skog</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 8621-2026 artfynd.xlsx
+++ b/artfynd/A 8621-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131759293</v>
       </c>
       <c r="B2" t="n">
-        <v>57896</v>
+        <v>57899</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>131758034</v>
       </c>
       <c r="B3" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>131758051</v>
       </c>
       <c r="B4" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
         <v>131758977</v>
       </c>
       <c r="B5" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         <v>131757950</v>
       </c>
       <c r="B6" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>131759073</v>
       </c>
       <c r="B7" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1328,7 +1328,7 @@
         <v>131759216</v>
       </c>
       <c r="B8" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1433,7 +1433,7 @@
         <v>131759058</v>
       </c>
       <c r="B9" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1538,7 +1538,7 @@
         <v>131758275</v>
       </c>
       <c r="B10" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1641,10 +1641,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131758963</v>
+        <v>131757839</v>
       </c>
       <c r="B11" t="n">
-        <v>79261</v>
+        <v>57902</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1652,30 +1652,31 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1683,10 +1684,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>774329</v>
+        <v>774162</v>
       </c>
       <c r="R11" t="n">
-        <v>7125645</v>
+        <v>7125616</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1713,12 +1714,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>förska ringhack på gran</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1727,7 +1733,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1746,10 +1751,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131757839</v>
+        <v>131758963</v>
       </c>
       <c r="B12" t="n">
-        <v>57899</v>
+        <v>79264</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1757,31 +1762,30 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1789,10 +1793,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>774162</v>
+        <v>774329</v>
       </c>
       <c r="R12" t="n">
-        <v>7125616</v>
+        <v>7125645</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1819,17 +1823,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>förska ringhack på gran</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1838,6 +1837,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1859,7 +1859,7 @@
         <v>131758995</v>
       </c>
       <c r="B13" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1973,7 +1973,7 @@
         <v>131759039</v>
       </c>
       <c r="B14" t="n">
-        <v>83107</v>
+        <v>83110</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2075,10 +2075,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131758858</v>
+        <v>131758780</v>
       </c>
       <c r="B15" t="n">
-        <v>57896</v>
+        <v>57902</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2086,16 +2086,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2106,11 +2106,7 @@
       <c r="I15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2118,10 +2114,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>774216</v>
+        <v>774139</v>
       </c>
       <c r="R15" t="n">
-        <v>7125596</v>
+        <v>7125579</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2148,24 +2144,24 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>hack i dött träd</t>
+          <t>bortfläkt bark på gran, kan vara gjort av tretåig hackspett som bevisligen födosöker i denna skog</t>
         </is>
       </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG15" t="b">
         <v>0</v>
@@ -2185,7 +2181,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131758780</v>
+        <v>131758858</v>
       </c>
       <c r="B16" t="n">
         <v>57899</v>
@@ -2196,16 +2192,16 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2216,7 +2212,11 @@
       <c r="I16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2224,10 +2224,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>774139</v>
+        <v>774216</v>
       </c>
       <c r="R16" t="n">
-        <v>7125579</v>
+        <v>7125596</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2254,24 +2254,24 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>bortfläkt bark på gran, kan vara gjort av tretåig hackspett som bevisligen födosöker i denna skog</t>
+          <t>hack i dött träd</t>
         </is>
       </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="b">
         <v>0</v>
@@ -2294,7 +2294,7 @@
         <v>131759091</v>
       </c>
       <c r="B17" t="n">
-        <v>83107</v>
+        <v>83110</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2399,7 +2399,7 @@
         <v>131759094</v>
       </c>
       <c r="B18" t="n">
-        <v>57896</v>
+        <v>57899</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2509,7 +2509,7 @@
         <v>131759162</v>
       </c>
       <c r="B19" t="n">
-        <v>57896</v>
+        <v>57899</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2619,7 +2619,7 @@
         <v>131758241</v>
       </c>
       <c r="B20" t="n">
-        <v>57896</v>
+        <v>57899</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2729,7 +2729,7 @@
         <v>131758953</v>
       </c>
       <c r="B21" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2834,7 +2834,7 @@
         <v>131758766</v>
       </c>
       <c r="B22" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 8621-2026 artfynd.xlsx
+++ b/artfynd/A 8621-2026 artfynd.xlsx
@@ -1005,10 +1005,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131758977</v>
+        <v>131757950</v>
       </c>
       <c r="B5" t="n">
-        <v>79264</v>
+        <v>57902</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1016,30 +1016,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1047,10 +1048,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>774353</v>
+        <v>774172</v>
       </c>
       <c r="R5" t="n">
-        <v>7125651</v>
+        <v>7125621</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1077,12 +1078,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1091,7 +1097,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1110,10 +1115,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131757950</v>
+        <v>131758977</v>
       </c>
       <c r="B6" t="n">
-        <v>57902</v>
+        <v>79264</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1121,31 +1126,30 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1153,10 +1157,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>774172</v>
+        <v>774353</v>
       </c>
       <c r="R6" t="n">
-        <v>7125621</v>
+        <v>7125651</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1183,17 +1187,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>färska ringhack på gran</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1202,6 +1201,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -2075,10 +2075,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131758780</v>
+        <v>131759091</v>
       </c>
       <c r="B15" t="n">
-        <v>57902</v>
+        <v>83110</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2086,27 +2086,30 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2114,10 +2117,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>774139</v>
+        <v>774532</v>
       </c>
       <c r="R15" t="n">
-        <v>7125579</v>
+        <v>7125635</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2144,25 +2147,21 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>bortfläkt bark på gran, kan vara gjort av tretåig hackspett som bevisligen födosöker i denna skog</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2181,10 +2180,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131758858</v>
+        <v>131758780</v>
       </c>
       <c r="B16" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2192,16 +2191,16 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2212,11 +2211,7 @@
       <c r="I16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2224,10 +2219,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>774216</v>
+        <v>774139</v>
       </c>
       <c r="R16" t="n">
-        <v>7125596</v>
+        <v>7125579</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2254,24 +2249,24 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>hack i dött träd</t>
+          <t>bortfläkt bark på gran, kan vara gjort av tretåig hackspett som bevisligen födosöker i denna skog</t>
         </is>
       </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG16" t="b">
         <v>0</v>
@@ -2291,10 +2286,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131759091</v>
+        <v>131758858</v>
       </c>
       <c r="B17" t="n">
-        <v>83110</v>
+        <v>57899</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2302,30 +2297,31 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1312</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2333,10 +2329,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>774532</v>
+        <v>774216</v>
       </c>
       <c r="R17" t="n">
-        <v>7125635</v>
+        <v>7125596</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2371,13 +2367,17 @@
           <t>2026-02-16</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>hack i dött träd</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 8621-2026 artfynd.xlsx
+++ b/artfynd/A 8621-2026 artfynd.xlsx
@@ -1005,10 +1005,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131757950</v>
+        <v>131758977</v>
       </c>
       <c r="B5" t="n">
-        <v>57902</v>
+        <v>79264</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1016,31 +1016,30 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1048,10 +1047,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>774172</v>
+        <v>774353</v>
       </c>
       <c r="R5" t="n">
-        <v>7125621</v>
+        <v>7125651</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1078,17 +1077,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>färska ringhack på gran</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1097,6 +1091,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1115,10 +1110,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131758977</v>
+        <v>131757950</v>
       </c>
       <c r="B6" t="n">
-        <v>79264</v>
+        <v>57902</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1126,30 +1121,31 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1157,10 +1153,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>774353</v>
+        <v>774172</v>
       </c>
       <c r="R6" t="n">
-        <v>7125651</v>
+        <v>7125621</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1187,12 +1183,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1201,7 +1202,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1641,10 +1641,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131757839</v>
+        <v>131758963</v>
       </c>
       <c r="B11" t="n">
-        <v>57902</v>
+        <v>79264</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1652,31 +1652,30 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1684,10 +1683,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>774162</v>
+        <v>774329</v>
       </c>
       <c r="R11" t="n">
-        <v>7125616</v>
+        <v>7125645</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1714,17 +1713,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>förska ringhack på gran</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1733,6 +1727,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1751,10 +1746,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131758963</v>
+        <v>131757839</v>
       </c>
       <c r="B12" t="n">
-        <v>79264</v>
+        <v>57902</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1762,30 +1757,31 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1793,10 +1789,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>774329</v>
+        <v>774162</v>
       </c>
       <c r="R12" t="n">
-        <v>7125645</v>
+        <v>7125616</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1823,12 +1819,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>förska ringhack på gran</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1837,7 +1838,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -2075,10 +2075,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131759091</v>
+        <v>131758858</v>
       </c>
       <c r="B15" t="n">
-        <v>83110</v>
+        <v>57899</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2086,30 +2086,31 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1312</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2117,10 +2118,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>774532</v>
+        <v>774216</v>
       </c>
       <c r="R15" t="n">
-        <v>7125635</v>
+        <v>7125596</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2155,13 +2156,17 @@
           <t>2026-02-16</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>hack i dött träd</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2286,10 +2291,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131758858</v>
+        <v>131759091</v>
       </c>
       <c r="B17" t="n">
-        <v>57899</v>
+        <v>83110</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2297,31 +2302,30 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>1312</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2329,10 +2333,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>774216</v>
+        <v>774532</v>
       </c>
       <c r="R17" t="n">
-        <v>7125596</v>
+        <v>7125635</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2367,17 +2371,13 @@
           <t>2026-02-16</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>hack i dött träd</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 8621-2026 artfynd.xlsx
+++ b/artfynd/A 8621-2026 artfynd.xlsx
@@ -2075,10 +2075,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131758858</v>
+        <v>131759091</v>
       </c>
       <c r="B15" t="n">
-        <v>57899</v>
+        <v>83110</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2086,31 +2086,30 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>1312</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2118,10 +2117,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>774216</v>
+        <v>774532</v>
       </c>
       <c r="R15" t="n">
-        <v>7125596</v>
+        <v>7125635</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2156,17 +2155,13 @@
           <t>2026-02-16</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>hack i dött träd</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2185,10 +2180,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131758780</v>
+        <v>131758858</v>
       </c>
       <c r="B16" t="n">
-        <v>57902</v>
+        <v>57899</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2196,16 +2191,16 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2216,7 +2211,11 @@
       <c r="I16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2224,10 +2223,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>774139</v>
+        <v>774216</v>
       </c>
       <c r="R16" t="n">
-        <v>7125579</v>
+        <v>7125596</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2254,24 +2253,24 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>bortfläkt bark på gran, kan vara gjort av tretåig hackspett som bevisligen födosöker i denna skog</t>
+          <t>hack i dött träd</t>
         </is>
       </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="b">
         <v>0</v>
@@ -2291,10 +2290,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131759091</v>
+        <v>131758780</v>
       </c>
       <c r="B17" t="n">
-        <v>83110</v>
+        <v>57902</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2302,30 +2301,27 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2333,10 +2329,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>774532</v>
+        <v>774139</v>
       </c>
       <c r="R17" t="n">
-        <v>7125635</v>
+        <v>7125579</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2363,21 +2359,25 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>bortfläkt bark på gran, kan vara gjort av tretåig hackspett som bevisligen födosöker i denna skog</t>
         </is>
       </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF17" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG17" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 8621-2026 artfynd.xlsx
+++ b/artfynd/A 8621-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131759293</v>
       </c>
       <c r="B2" t="n">
-        <v>57899</v>
+        <v>57901</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>131758034</v>
       </c>
       <c r="B3" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>131758051</v>
       </c>
       <c r="B4" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
         <v>131758977</v>
       </c>
       <c r="B5" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         <v>131757950</v>
       </c>
       <c r="B6" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>131759073</v>
       </c>
       <c r="B7" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1328,7 +1328,7 @@
         <v>131759216</v>
       </c>
       <c r="B8" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1433,7 +1433,7 @@
         <v>131759058</v>
       </c>
       <c r="B9" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1538,7 +1538,7 @@
         <v>131758275</v>
       </c>
       <c r="B10" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1641,10 +1641,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131758963</v>
+        <v>131757839</v>
       </c>
       <c r="B11" t="n">
-        <v>79264</v>
+        <v>57904</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1652,30 +1652,31 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1683,10 +1684,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>774329</v>
+        <v>774162</v>
       </c>
       <c r="R11" t="n">
-        <v>7125645</v>
+        <v>7125616</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1713,12 +1714,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>förska ringhack på gran</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1727,7 +1733,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1746,10 +1751,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131757839</v>
+        <v>131758963</v>
       </c>
       <c r="B12" t="n">
-        <v>57902</v>
+        <v>79266</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1757,31 +1762,30 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1789,10 +1793,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>774162</v>
+        <v>774329</v>
       </c>
       <c r="R12" t="n">
-        <v>7125616</v>
+        <v>7125645</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1819,17 +1823,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>förska ringhack på gran</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1838,6 +1837,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1859,7 +1859,7 @@
         <v>131758995</v>
       </c>
       <c r="B13" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1973,7 +1973,7 @@
         <v>131759039</v>
       </c>
       <c r="B14" t="n">
-        <v>83110</v>
+        <v>83112</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2078,7 +2078,7 @@
         <v>131759091</v>
       </c>
       <c r="B15" t="n">
-        <v>83110</v>
+        <v>83112</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2183,7 +2183,7 @@
         <v>131758858</v>
       </c>
       <c r="B16" t="n">
-        <v>57899</v>
+        <v>57901</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2293,7 +2293,7 @@
         <v>131758780</v>
       </c>
       <c r="B17" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2399,7 +2399,7 @@
         <v>131759094</v>
       </c>
       <c r="B18" t="n">
-        <v>57899</v>
+        <v>57901</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2509,7 +2509,7 @@
         <v>131759162</v>
       </c>
       <c r="B19" t="n">
-        <v>57899</v>
+        <v>57901</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2619,7 +2619,7 @@
         <v>131758241</v>
       </c>
       <c r="B20" t="n">
-        <v>57899</v>
+        <v>57901</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2729,7 +2729,7 @@
         <v>131758953</v>
       </c>
       <c r="B21" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2834,7 +2834,7 @@
         <v>131758766</v>
       </c>
       <c r="B22" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 8621-2026 artfynd.xlsx
+++ b/artfynd/A 8621-2026 artfynd.xlsx
@@ -1005,10 +1005,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131758977</v>
+        <v>131757950</v>
       </c>
       <c r="B5" t="n">
-        <v>79266</v>
+        <v>57904</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1016,30 +1016,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1047,10 +1048,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>774353</v>
+        <v>774172</v>
       </c>
       <c r="R5" t="n">
-        <v>7125651</v>
+        <v>7125621</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1077,12 +1078,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1091,7 +1097,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1110,10 +1115,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131757950</v>
+        <v>131758977</v>
       </c>
       <c r="B6" t="n">
-        <v>57904</v>
+        <v>79266</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1121,31 +1126,30 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1153,10 +1157,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>774172</v>
+        <v>774353</v>
       </c>
       <c r="R6" t="n">
-        <v>7125621</v>
+        <v>7125651</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1183,17 +1187,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>färska ringhack på gran</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1202,6 +1201,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 8621-2026 artfynd.xlsx
+++ b/artfynd/A 8621-2026 artfynd.xlsx
@@ -1005,10 +1005,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131757950</v>
+        <v>131758977</v>
       </c>
       <c r="B5" t="n">
-        <v>57904</v>
+        <v>79266</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1016,31 +1016,30 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1048,10 +1047,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>774172</v>
+        <v>774353</v>
       </c>
       <c r="R5" t="n">
-        <v>7125621</v>
+        <v>7125651</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1078,17 +1077,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>färska ringhack på gran</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1097,6 +1091,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1115,10 +1110,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131758977</v>
+        <v>131757950</v>
       </c>
       <c r="B6" t="n">
-        <v>79266</v>
+        <v>57904</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1126,30 +1121,31 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1157,10 +1153,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>774353</v>
+        <v>774172</v>
       </c>
       <c r="R6" t="n">
-        <v>7125651</v>
+        <v>7125621</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1187,12 +1183,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1201,7 +1202,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 8621-2026 artfynd.xlsx
+++ b/artfynd/A 8621-2026 artfynd.xlsx
@@ -1005,10 +1005,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131758977</v>
+        <v>131757950</v>
       </c>
       <c r="B5" t="n">
-        <v>79266</v>
+        <v>57904</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1016,30 +1016,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1047,10 +1048,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>774353</v>
+        <v>774172</v>
       </c>
       <c r="R5" t="n">
-        <v>7125651</v>
+        <v>7125621</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1077,12 +1078,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1091,7 +1097,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1110,10 +1115,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131757950</v>
+        <v>131758977</v>
       </c>
       <c r="B6" t="n">
-        <v>57904</v>
+        <v>79266</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1121,31 +1126,30 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1153,10 +1157,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>774172</v>
+        <v>774353</v>
       </c>
       <c r="R6" t="n">
-        <v>7125621</v>
+        <v>7125651</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1183,17 +1187,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>färska ringhack på gran</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1202,6 +1201,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1641,10 +1641,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131757839</v>
+        <v>131758963</v>
       </c>
       <c r="B11" t="n">
-        <v>57904</v>
+        <v>79266</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1652,31 +1652,30 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1684,10 +1683,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>774162</v>
+        <v>774329</v>
       </c>
       <c r="R11" t="n">
-        <v>7125616</v>
+        <v>7125645</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1714,17 +1713,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>förska ringhack på gran</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1733,6 +1727,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1751,10 +1746,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131758963</v>
+        <v>131757839</v>
       </c>
       <c r="B12" t="n">
-        <v>79266</v>
+        <v>57904</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1762,30 +1757,31 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1793,10 +1789,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>774329</v>
+        <v>774162</v>
       </c>
       <c r="R12" t="n">
-        <v>7125645</v>
+        <v>7125616</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1823,12 +1819,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>förska ringhack på gran</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1837,7 +1838,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 8621-2026 artfynd.xlsx
+++ b/artfynd/A 8621-2026 artfynd.xlsx
@@ -785,7 +785,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131758034</v>
+        <v>131758051</v>
       </c>
       <c r="B3" t="n">
         <v>57948</v>
@@ -818,7 +818,7 @@
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -828,10 +828,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>774190</v>
+        <v>774217</v>
       </c>
       <c r="R3" t="n">
-        <v>7125644</v>
+        <v>7125691</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -868,7 +868,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>äldre ringhack högt upp i gran</t>
+          <t>färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -895,7 +895,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131758051</v>
+        <v>131758034</v>
       </c>
       <c r="B4" t="n">
         <v>57948</v>
@@ -928,7 +928,7 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -938,10 +938,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>774217</v>
+        <v>774190</v>
       </c>
       <c r="R4" t="n">
-        <v>7125691</v>
+        <v>7125644</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -978,7 +978,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>färska ringhack på gran</t>
+          <t>äldre ringhack högt upp i gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1005,10 +1005,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131758977</v>
+        <v>131757950</v>
       </c>
       <c r="B5" t="n">
-        <v>79315</v>
+        <v>57948</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1016,30 +1016,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1047,10 +1048,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>774353</v>
+        <v>774172</v>
       </c>
       <c r="R5" t="n">
-        <v>7125651</v>
+        <v>7125621</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1077,12 +1078,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1091,7 +1097,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1110,10 +1115,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131757950</v>
+        <v>131758977</v>
       </c>
       <c r="B6" t="n">
-        <v>57948</v>
+        <v>79317</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1121,31 +1126,30 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1153,10 +1157,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>774172</v>
+        <v>774353</v>
       </c>
       <c r="R6" t="n">
-        <v>7125621</v>
+        <v>7125651</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1183,17 +1187,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>färska ringhack på gran</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1202,6 +1201,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1223,7 +1223,7 @@
         <v>131759073</v>
       </c>
       <c r="B7" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1328,7 +1328,7 @@
         <v>131759216</v>
       </c>
       <c r="B8" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1433,7 +1433,7 @@
         <v>131759058</v>
       </c>
       <c r="B9" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1644,7 +1644,7 @@
         <v>131758963</v>
       </c>
       <c r="B11" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1859,7 +1859,7 @@
         <v>131758995</v>
       </c>
       <c r="B13" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1973,7 +1973,7 @@
         <v>131759039</v>
       </c>
       <c r="B14" t="n">
-        <v>83161</v>
+        <v>83163</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2075,10 +2075,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131758858</v>
+        <v>131759091</v>
       </c>
       <c r="B15" t="n">
-        <v>57945</v>
+        <v>83163</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2086,31 +2086,30 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>1312</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2118,10 +2117,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>774216</v>
+        <v>774532</v>
       </c>
       <c r="R15" t="n">
-        <v>7125596</v>
+        <v>7125635</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2156,17 +2155,13 @@
           <t>2026-02-16</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>hack i dött träd</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2185,10 +2180,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131759091</v>
+        <v>131758780</v>
       </c>
       <c r="B16" t="n">
-        <v>83161</v>
+        <v>57948</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2196,30 +2191,27 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2227,10 +2219,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>774532</v>
+        <v>774139</v>
       </c>
       <c r="R16" t="n">
-        <v>7125635</v>
+        <v>7125579</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2257,21 +2249,25 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>bortfläkt bark på gran, kan vara gjort av tretåig hackspett som bevisligen födosöker i denna skog</t>
         </is>
       </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF16" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2290,10 +2286,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131758780</v>
+        <v>131758858</v>
       </c>
       <c r="B17" t="n">
-        <v>57948</v>
+        <v>57945</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2301,16 +2297,16 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2321,7 +2317,11 @@
       <c r="I17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2329,10 +2329,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>774139</v>
+        <v>774216</v>
       </c>
       <c r="R17" t="n">
-        <v>7125579</v>
+        <v>7125596</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2359,24 +2359,24 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>bortfläkt bark på gran, kan vara gjort av tretåig hackspett som bevisligen födosöker i denna skog</t>
+          <t>hack i dött träd</t>
         </is>
       </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="b">
         <v>0</v>
@@ -2729,7 +2729,7 @@
         <v>131758953</v>
       </c>
       <c r="B21" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 8621-2026 artfynd.xlsx
+++ b/artfynd/A 8621-2026 artfynd.xlsx
@@ -2075,10 +2075,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131759091</v>
+        <v>131758780</v>
       </c>
       <c r="B15" t="n">
-        <v>83163</v>
+        <v>57948</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2086,30 +2086,27 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2117,10 +2114,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>774532</v>
+        <v>774139</v>
       </c>
       <c r="R15" t="n">
-        <v>7125635</v>
+        <v>7125579</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2147,21 +2144,25 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>bortfläkt bark på gran, kan vara gjort av tretåig hackspett som bevisligen födosöker i denna skog</t>
         </is>
       </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF15" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2180,10 +2181,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131758780</v>
+        <v>131759091</v>
       </c>
       <c r="B16" t="n">
-        <v>57948</v>
+        <v>83163</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2191,27 +2192,30 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2219,10 +2223,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>774139</v>
+        <v>774532</v>
       </c>
       <c r="R16" t="n">
-        <v>7125579</v>
+        <v>7125635</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2249,25 +2253,21 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>bortfläkt bark på gran, kan vara gjort av tretåig hackspett som bevisligen födosöker i denna skog</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 8621-2026 artfynd.xlsx
+++ b/artfynd/A 8621-2026 artfynd.xlsx
@@ -1005,10 +1005,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131757950</v>
+        <v>131758977</v>
       </c>
       <c r="B5" t="n">
-        <v>57948</v>
+        <v>79317</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1016,31 +1016,30 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1048,10 +1047,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>774172</v>
+        <v>774353</v>
       </c>
       <c r="R5" t="n">
-        <v>7125621</v>
+        <v>7125651</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1078,17 +1077,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>färska ringhack på gran</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1097,6 +1091,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1115,10 +1110,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131758977</v>
+        <v>131757950</v>
       </c>
       <c r="B6" t="n">
-        <v>79317</v>
+        <v>57948</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1126,30 +1121,31 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1157,10 +1153,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>774353</v>
+        <v>774172</v>
       </c>
       <c r="R6" t="n">
-        <v>7125651</v>
+        <v>7125621</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1187,12 +1183,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1201,7 +1202,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 8621-2026 artfynd.xlsx
+++ b/artfynd/A 8621-2026 artfynd.xlsx
@@ -785,7 +785,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131758051</v>
+        <v>131758034</v>
       </c>
       <c r="B3" t="n">
         <v>57948</v>
@@ -818,7 +818,7 @@
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -828,10 +828,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>774217</v>
+        <v>774190</v>
       </c>
       <c r="R3" t="n">
-        <v>7125691</v>
+        <v>7125644</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -868,7 +868,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>färska ringhack på gran</t>
+          <t>äldre ringhack högt upp i gran</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -895,7 +895,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131758034</v>
+        <v>131758051</v>
       </c>
       <c r="B4" t="n">
         <v>57948</v>
@@ -928,7 +928,7 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -938,10 +938,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>774190</v>
+        <v>774217</v>
       </c>
       <c r="R4" t="n">
-        <v>7125644</v>
+        <v>7125691</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -978,7 +978,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>äldre ringhack högt upp i gran</t>
+          <t>färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1641,10 +1641,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131758963</v>
+        <v>131757839</v>
       </c>
       <c r="B11" t="n">
-        <v>79317</v>
+        <v>57948</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1652,30 +1652,31 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1683,10 +1684,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>774329</v>
+        <v>774162</v>
       </c>
       <c r="R11" t="n">
-        <v>7125645</v>
+        <v>7125616</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1713,12 +1714,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>förska ringhack på gran</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1727,7 +1733,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1746,10 +1751,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131757839</v>
+        <v>131758963</v>
       </c>
       <c r="B12" t="n">
-        <v>57948</v>
+        <v>79317</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1757,31 +1762,30 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1789,10 +1793,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>774162</v>
+        <v>774329</v>
       </c>
       <c r="R12" t="n">
-        <v>7125616</v>
+        <v>7125645</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1819,17 +1823,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>förska ringhack på gran</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1838,6 +1837,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -2075,10 +2075,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131758780</v>
+        <v>131758858</v>
       </c>
       <c r="B15" t="n">
-        <v>57948</v>
+        <v>57945</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2086,16 +2086,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2106,7 +2106,11 @@
       <c r="I15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2114,10 +2118,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>774139</v>
+        <v>774216</v>
       </c>
       <c r="R15" t="n">
-        <v>7125579</v>
+        <v>7125596</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2144,24 +2148,24 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>bortfläkt bark på gran, kan vara gjort av tretåig hackspett som bevisligen födosöker i denna skog</t>
+          <t>hack i dött träd</t>
         </is>
       </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="b">
         <v>0</v>
@@ -2181,10 +2185,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131759091</v>
+        <v>131758780</v>
       </c>
       <c r="B16" t="n">
-        <v>83163</v>
+        <v>57948</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2192,30 +2196,27 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2223,10 +2224,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>774532</v>
+        <v>774139</v>
       </c>
       <c r="R16" t="n">
-        <v>7125635</v>
+        <v>7125579</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2253,21 +2254,25 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>bortfläkt bark på gran, kan vara gjort av tretåig hackspett som bevisligen födosöker i denna skog</t>
         </is>
       </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF16" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2286,10 +2291,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131758858</v>
+        <v>131759091</v>
       </c>
       <c r="B17" t="n">
-        <v>57945</v>
+        <v>83163</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2297,31 +2302,30 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>1312</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2329,10 +2333,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>774216</v>
+        <v>774532</v>
       </c>
       <c r="R17" t="n">
-        <v>7125596</v>
+        <v>7125635</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2367,17 +2371,13 @@
           <t>2026-02-16</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>hack i dött träd</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
